--- a/1-wiki-资料沉淀/业务调研事项记录.xlsx
+++ b/1-wiki-资料沉淀/业务调研事项记录.xlsx
@@ -1,25 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zihaoguo/Desktop/上海济工/scos_proj/1-wiki-资料沉淀/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01114F92-F00E-D94E-A893-275E609041FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="1060" yWindow="820" windowWidth="28100" windowHeight="17360" xr2:uid="{CE77F15F-EC5A-5547-8870-BA123778C434}"/>
+    <workbookView windowWidth="29100" windowHeight="13380"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -31,57 +22,66 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="53">
+  <si>
+    <t>业务模块</t>
+  </si>
+  <si>
+    <t>子模块</t>
+  </si>
+  <si>
+    <t>事项类型</t>
+  </si>
+  <si>
+    <t>事项描述</t>
+  </si>
+  <si>
+    <t>是否确认</t>
+  </si>
+  <si>
+    <t>结论和解决方案</t>
+  </si>
   <si>
     <t>备注</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>业务模块</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>子模块</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>采购优化</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>采购计划滚动周期</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>业务调研</t>
   </si>
   <si>
     <t>采购计划的粒度和滚动周期是什么？我们目前设定为周检查</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是</t>
   </si>
   <si>
     <t>实时检查，有需求就更新采购计划</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>事项描述</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>供应商评价相关数据</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>需求确认</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">采购决策模型只以成本为目标，
 目前设计供应商主要展示如下评价指标：
 - 质量合格率
@@ -97,23 +97,26 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>系统提供供应商进入候选池条件筛选，主要筛选项：采购价格区间、运费区间、质量合格率下限、准时交付率下限等。</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>事项类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>指标仅做展示，不根据评价指标对供应商做强制筛选</t>
   </si>
   <si>
     <t>采购成本</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>目前设计中采购总成本只包含四部分：供应商报价、运输成本、仓储成本、账期成本、</t>
     </r>
     <r>
@@ -121,7 +124,6 @@
         <sz val="12"/>
         <color rgb="FFFF0000"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>包装袋回收成本</t>
@@ -131,7 +133,6 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -145,74 +146,63 @@
 a_{ij}=c_{ij}\times 资金成本率\times\frac{账期天数_{ij}}{365}
 $$</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>账期成本折算方式无问题；
+新增决策变量：包装袋回收成本，即如果包装袋可以回收，可以节省部分成本</t>
   </si>
   <si>
     <t>供应商选择</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>提供供应商强制选择功能和供应商供应数量的上下限设置功能</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>是否确认</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>是</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>库存优化</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>页面展示</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>新增需求</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>1. 展示当前的在途采购订单 + 库存还能做多少成品，以及还能支持生产多少天（暂定展示能做每种成品各多少量）
 2. 可用库存展示，需要拆分成 在库实物库存、在途实物库存、在手未执行合同量
 3. 供应商展示合同价</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>库存优化</t>
   </si>
   <si>
     <t>冷启动</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>项目投运初期历史数据不足时，是否可使用同类工厂历史业务数据进行冷启动？还是人工设定参数？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>前期人工设定参数，系统启用时会有历史数据</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>库存计划更新频率</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>当前暂按“月度更新再补货点和目标库存、日度更新库存水位并判断是否需要补货、异常手动触发重算”的设计。需要确认当做月度计划管理时，库存模块是否需要在月初给出当月总共的补货需求？
 库存优化需要输出两套结果：第一是在每月月末输出次月总补货量，第二是在每日库存核验时输出每日的成品补货量。
 月总补货量是否下探到周维度？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>下探到周，库存优化有两版，分别为周计划和日计划</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>库存容量上限问题</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>由于一个成品罐在当前成品排完后可以继续流入其他成品，导致成品的库存容量存在共享的情况，我们应该如何判断一个成品的库存容量上限？库存容量会影响我们下发的补货量
 可能的解决方案：根据成品未来的需求占比分配总体库存容量；</t>
     </r>
@@ -222,57 +212,46 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>或者系统先维护“成品—可用储罐”映射，例如成品A只能使用1—10号罐、成品B只能使用11—20号罐，则两种成品的容量分别计算，不能直接使用全厂总容量。</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>需要设计，目前能想到的是：1. 首先按照无库容上限计算补货量，然后超出部分按照商品服务水平设定从低到高依次减少补货量；2. 直接用共享库容的方式求解</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>成品流入储罐限制</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>一个生产批次能否拆分进入多个罐？同一储罐能否混装不同生产批次，能否在原有库存上继续补入？该问题会影响库存容量校验、批次追溯和入罐冲突判断</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>1. 可以合批（多个qc罐进入一个成品罐）但不能一个qc罐进入多个成品罐
 2. 存在在库库存转化为在途库存的情况（闲置成品罐库存会返回qc罐）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>库存优化覆盖SKU范围</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>结论和解决方案</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>标书中的库存优化覆盖SKU范围包括原料、在制品、产成品和副产品，目前业务蓝图限定为成品库存，是否已确认按成品范围建设和验收？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>库存优化只做成品
 其他SKU做库存预警</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>生产提前期</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>由于是连续生产，待生产时间忽略不计；开车订单生产时间较长</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">
 - 开始时间：生产补充需求审批完成、正式进入待生产状态的时间。
 - 结束时间：成品生产完成、质检放行并进入可用库存的时间。
@@ -285,7 +264,6 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>生产等待时间</t>
@@ -295,63 +273,231 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <family val="2"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>+生产时间+成品入库时间
 其中，质检放行时间普遍是2h完成，日内完成，不考虑在内</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>由于是连续生产，待生产时间忽略不计；开车订单生产时间较长</t>
   </si>
   <si>
     <t>出货计划</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>业务调研</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>出货计划的提前期和展望期？</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>出货计划的提前期和展望期？是否有锁定期？临时需求怎么处理？</t>
   </si>
   <si>
     <t>否</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>需要跟CRM确认</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>账期成本折算方式无问题；
-新增决策变量：包装袋回收成本，即如果包装袋可以回收，可以节省部分成本</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>指标仅做展示，不根据评价指标对供应商做强制筛选</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>补货最小批量</t>
+  </si>
+  <si>
+    <t>每次流入成品罐是否需要灌满整罐？是否需要按整罐补货？如果封罐才能售卖，不能边进边出，封罐的水位线是否有要求？</t>
+  </si>
+  <si>
+    <t>库存计划锁定期</t>
+  </si>
+  <si>
+    <t>生产端需要提前安排生产计划，
+库存计划需要锁定期，建议锁定期定为多长时间？</t>
+  </si>
+  <si>
+    <t>有锁定期的库存优化方案：
+1. 库存优化参数（人工设置：不同成品服务水平人工设置；算法计算：每日再补货点、目标库存、安全库存）更新协同频率：每月随销售计划更新（每月25日更新并完成协同调整），更新后会作为周维度总补货量和日维度补货量明细结果计算的输入数据
+2. 周维度总补货量和日维度补货量明细生成业务逻辑：
+- 滚动周期：周维度滚动更新
+- 展望期：未来一个月
+- 锁定期：1周（7天，目前暂定）
+- 输入：每日再补货点、目标库存、安全库存、起始库存水平（在库+在途）、出货计划（提前期、展望期和锁定期待确认）、月销售计划（均分到日或者按照日历拆分到日）、其他约束条件（库容上限、单次补货最小批量等）
+- 输出：展望期内每周的总补货量、展望期内每日的补货计划（补货量和补货时间）
+- 更新计算逻辑：
+a. 基于起始库存、每日再补货点、目标库存、安全库存、每日预计出货量（有出货计划用出货计划，没有用拆分到日的销售计划）和约束条件计算推演展望期内的每日的补货量，即展望期内每日的补货计划（包括补货量和补货时间）；
+b. 按周维度汇总，输出展望期内每周的总补货量；
+c. 锁定期：当周总补货量和每日补货计划和生产端协同后进行锁定，锁定期内不再更新；如果出货计划或者销售计划有调整，只更新展望期内除了锁定期以外的补货计划
+d. 更新机制：次周周初更新下一个展望期内的补货计划，以上述方式滚动</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="24">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="2"/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -359,34 +505,210 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FFFF0000"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -395,124 +717,416 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
+      <left style="medium">
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
+      <top style="medium">
+        <color auto="1"/>
       </top>
-      <bottom style="thin">
-        <color indexed="64"/>
+      <bottom style="medium">
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
+      <right style="medium">
+        <color auto="1"/>
       </right>
       <top style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
-      <right style="medium">
-        <color indexed="64"/>
+      <right style="thin">
+        <color auto="1"/>
       </right>
-      <top style="medium">
-        <color indexed="64"/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
       </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="medium">
-        <color indexed="64"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -561,7 +1175,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Display"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -594,26 +1208,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Narrow"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -646,23 +1243,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -824,300 +1404,329 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32B83268-D629-014D-8C65-95AD0BC73CC9}">
-  <dimension ref="A1:G13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G15"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="17.6" outlineLevelCol="6"/>
   <cols>
-    <col min="2" max="2" width="20.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.6640625" customWidth="1"/>
-    <col min="4" max="4" width="62.83203125" customWidth="1"/>
-    <col min="5" max="5" width="10.83203125" customWidth="1"/>
-    <col min="6" max="6" width="69.83203125" customWidth="1"/>
+    <col min="2" max="2" width="20.8333333333333" customWidth="1"/>
+    <col min="3" max="3" width="18.6666666666667" customWidth="1"/>
+    <col min="4" max="4" width="62.8333333333333" customWidth="1"/>
+    <col min="5" max="5" width="10.8333333333333" customWidth="1"/>
+    <col min="6" max="6" width="69.8333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="17" thickBot="1">
-      <c r="A1" s="5" t="s">
+    <row r="1" ht="18.35" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" ht="18" spans="1:7">
+      <c r="A2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="F2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="4"/>
+    </row>
+    <row r="3" ht="229" spans="1:7">
+      <c r="A3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="B3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="G3" s="6"/>
+    </row>
+    <row r="4" ht="300" spans="1:7">
+      <c r="A4" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="6"/>
+    </row>
+    <row r="5" ht="18" spans="1:7">
+      <c r="A5" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+    </row>
+    <row r="6" ht="88" spans="1:7">
+      <c r="A6" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+    </row>
+    <row r="7" ht="36" spans="1:7">
+      <c r="A7" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" s="6"/>
+    </row>
+    <row r="8" ht="141" spans="1:7">
+      <c r="A8" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G8" s="6"/>
+    </row>
+    <row r="9" ht="141" spans="1:7">
+      <c r="A9" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G9" s="6"/>
+    </row>
+    <row r="10" ht="53" spans="1:7">
+      <c r="A10" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="G1" s="7" t="s">
-        <v>0</v>
-      </c>
+      <c r="C10" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="G10" s="6"/>
     </row>
-    <row r="2" spans="1:7" ht="17">
-      <c r="A2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="3" t="s">
+    <row r="11" ht="36" spans="1:7">
+      <c r="A11" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G11" s="6"/>
+    </row>
+    <row r="12" ht="176" spans="1:7">
+      <c r="A12" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="3"/>
+      <c r="E12" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="G12" s="6"/>
     </row>
-    <row r="3" spans="1:7" ht="221">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="1" t="s">
+    <row r="13" ht="18" spans="1:7">
+      <c r="A13" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="1" t="s">
+      <c r="D13" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="F13" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="G3" s="1"/>
+      <c r="G13" s="6"/>
     </row>
-    <row r="4" spans="1:7" ht="272">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G4" s="1"/>
+    <row r="14" ht="36" spans="1:7">
+      <c r="A14" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="E14" s="9"/>
+      <c r="F14" s="10"/>
     </row>
-    <row r="5" spans="1:7" ht="17">
-      <c r="A5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="1" t="s">
+    <row r="15" ht="408" customHeight="1" spans="1:7">
+      <c r="A15" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-    </row>
-    <row r="6" spans="1:7" ht="85">
-      <c r="A6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-    </row>
-    <row r="7" spans="1:7" ht="34">
-      <c r="A7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G7" s="1"/>
-    </row>
-    <row r="8" spans="1:7" ht="136">
-      <c r="A8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G8" s="1"/>
-    </row>
-    <row r="9" spans="1:7" ht="136">
-      <c r="A9" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G9" s="1"/>
-    </row>
-    <row r="10" spans="1:7" ht="51">
-      <c r="A10" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G10" s="1"/>
-    </row>
-    <row r="11" spans="1:7" ht="34">
-      <c r="A11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G11" s="1"/>
-    </row>
-    <row r="12" spans="1:7" ht="170">
-      <c r="A12" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="G12" s="1"/>
-    </row>
-    <row r="13" spans="1:7" ht="17">
-      <c r="A13" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="G13" s="1"/>
+      <c r="D15" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="E15" s="9"/>
+      <c r="F15" s="10" t="s">
+        <v>52</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/1-wiki-资料沉淀/业务调研事项记录.xlsx
+++ b/1-wiki-资料沉淀/业务调研事项记录.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29100" windowHeight="13380"/>
+    <workbookView windowHeight="16760"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -750,13 +750,11 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="medium">
+      <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
+      <top/>
+      <bottom style="thin">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -768,7 +766,9 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -778,13 +778,13 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="thin">
+      <right style="medium">
         <color auto="1"/>
       </right>
-      <top style="thin">
+      <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -1037,7 +1037,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1059,17 +1059,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1439,289 +1433,289 @@
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" ht="18" spans="1:7">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="4"/>
+      <c r="G2" s="3"/>
     </row>
     <row r="3" ht="229" spans="1:7">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="6"/>
+      <c r="G3" s="4"/>
     </row>
     <row r="4" ht="300" spans="1:7">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="6"/>
+      <c r="G4" s="4"/>
     </row>
     <row r="5" ht="18" spans="1:7">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
     </row>
     <row r="6" ht="88" spans="1:7">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
     </row>
     <row r="7" ht="36" spans="1:7">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="6"/>
+      <c r="G7" s="4"/>
     </row>
     <row r="8" ht="141" spans="1:7">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G8" s="6"/>
+      <c r="G8" s="4"/>
     </row>
     <row r="9" ht="141" spans="1:7">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="G9" s="6"/>
+      <c r="G9" s="4"/>
     </row>
     <row r="10" ht="53" spans="1:7">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G10" s="6"/>
+      <c r="G10" s="4"/>
     </row>
     <row r="11" ht="36" spans="1:7">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G11" s="6"/>
+      <c r="G11" s="4"/>
     </row>
     <row r="12" ht="176" spans="1:7">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="F12" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="G12" s="6"/>
+      <c r="G12" s="4"/>
     </row>
     <row r="13" ht="18" spans="1:7">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" s="4" t="s">
         <v>46</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="G13" s="6"/>
+      <c r="G13" s="4"/>
     </row>
-    <row r="14" ht="36" spans="1:7">
-      <c r="A14" s="9" t="s">
+    <row r="14" ht="36" spans="1:6">
+      <c r="A14" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D14" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="E14" s="9"/>
-      <c r="F14" s="10"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="5"/>
     </row>
-    <row r="15" ht="408" customHeight="1" spans="1:7">
-      <c r="A15" s="9" t="s">
+    <row r="15" ht="408" customHeight="1" spans="1:6">
+      <c r="A15" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D15" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E15" s="9"/>
-      <c r="F15" s="10" t="s">
+      <c r="E15" s="4"/>
+      <c r="F15" s="5" t="s">
         <v>52</v>
       </c>
     </row>

--- a/1-wiki-资料沉淀/业务调研事项记录.xlsx
+++ b/1-wiki-资料沉淀/业务调研事项记录.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16760"/>
+    <workbookView windowWidth="29100" windowHeight="13380"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="122">
   <si>
     <t>业务模块</t>
   </si>
@@ -36,6 +36,9 @@
   </si>
   <si>
     <t>事项类型</t>
+  </si>
+  <si>
+    <t>事项简述</t>
   </si>
   <si>
     <t>事项描述</t>
@@ -290,16 +293,16 @@
     <t>出货计划的提前期和展望期？是否有锁定期？临时需求怎么处理？</t>
   </si>
   <si>
-    <t>否</t>
-  </si>
-  <si>
-    <t>需要跟CRM确认</t>
+    <t>展望期是1周，准确率90%，每周五做下周的周出货计划，每日做更精准的修正</t>
   </si>
   <si>
     <t>补货最小批量</t>
   </si>
   <si>
     <t>每次流入成品罐是否需要灌满整罐？是否需要按整罐补货？如果封罐才能售卖，不能边进边出，封罐的水位线是否有要求？</t>
+  </si>
+  <si>
+    <t>没有硬性要求，但区分淡旺季：旺季为了加速库存周转和满足出货频率，可以低液位封罐售卖；淡季由于周转慢，一般是在92%以上的液位封罐</t>
   </si>
   <si>
     <t>库存计划锁定期</t>
@@ -322,6 +325,220 @@
 b. 按周维度汇总，输出展望期内每周的总补货量；
 c. 锁定期：当周总补货量和每日补货计划和生产端协同后进行锁定，锁定期内不再更新；如果出货计划或者销售计划有调整，只更新展望期内除了锁定期以外的补货计划
 d. 更新机制：次周周初更新下一个展望期内的补货计划，以上述方式滚动</t>
+  </si>
+  <si>
+    <t>成本分摊</t>
+  </si>
+  <si>
+    <t>批次管理</t>
+  </si>
+  <si>
+    <t>问题确认</t>
+  </si>
+  <si>
+    <t>工艺转化</t>
+  </si>
+  <si>
+    <t>每一批物料在各工艺产出的质量怎么获取？收率是怎么获取？</t>
+  </si>
+  <si>
+    <t>糖化罐和QC罐进出</t>
+  </si>
+  <si>
+    <t>12个糖化罐是同时排出还是依次排出？
+QC罐是同时进料还是依次进料？</t>
+  </si>
+  <si>
+    <t>流量</t>
+  </si>
+  <si>
+    <t>管道和设备是全流还是半流还是变化的？
+如果没有生产负荷调整，单位时间的流量是恒定的还是变化？
+管道和设备里面的压力是恒定的吗？
+在管道中的流量和在设备中的流量是一样的吗？</t>
+  </si>
+  <si>
+    <t>质检</t>
+  </si>
+  <si>
+    <t>任意流程中质检不合格的批次怎么处理？</t>
+  </si>
+  <si>
+    <t>批次状态</t>
+  </si>
+  <si>
+    <t>批次状态异常的含义是什么？异常如果不参与追溯会导致整体成本出现问题</t>
+  </si>
+  <si>
+    <t>设备有效容积</t>
+  </si>
+  <si>
+    <t>设备的有效容积怎么获取？
+有效容积是质量吗？流体密度怎么计算？</t>
+  </si>
+  <si>
+    <t>误差累计</t>
+  </si>
+  <si>
+    <t>如果每个批次以上一批次终点作为下一批次起点，而过程时间又根据某一时刻平均流量计算，则一次流量误差会沿后续所有窗口累积。停机、降负荷、仪表缺数或重新计算还可能改变已生成的批次边界。</t>
+  </si>
+  <si>
+    <t>第3层：投料批次</t>
+  </si>
+  <si>
+    <t>淀粉乳罐</t>
+  </si>
+  <si>
+    <t>投料口后的三个罐（溶粉罐、乳罐、接收罐）是否有必要建立批次？</t>
+  </si>
+  <si>
+    <t>投料批次连续</t>
+  </si>
+  <si>
+    <t>需要通过一些预警机制确保投料时连续使用同一批次直到该批次用完</t>
+  </si>
+  <si>
+    <t>平均流量</t>
+  </si>
+  <si>
+    <t>投料过程中取的质量流量计是取淀粉乳接收罐后的质量流量计吗？
+过程时间中取批次启动时质量流量计的平均流量：批次启动时间是按照投料开始时间算吗？平均流量是需要设定某段时间流量波动性下降到某一阈值再计算平均流量吗？</t>
+  </si>
+  <si>
+    <t>第4层：糖化批次</t>
+  </si>
+  <si>
+    <t>阀门切换</t>
+  </si>
+  <si>
+    <t>DCS进罐阀门切换记录编号：阀门切换是指由关到开或者由开到关的状态切换吗？</t>
+  </si>
+  <si>
+    <t>进入糖化批次重量</t>
+  </si>
+  <si>
+    <t>怎么计算即将进入糖化批次的体积或者重量？需要用体积关联上游批次</t>
+  </si>
+  <si>
+    <t>糖化罐进液顺序</t>
+  </si>
+  <si>
+    <t>糖化罐同一时间是否只有一个罐开放？即装满后才会开放下一个糖化罐</t>
+  </si>
+  <si>
+    <t>批次多对多</t>
+  </si>
+  <si>
+    <t>由于糖化罐的容积和上游每个批次的体积不能完全对齐，可能会导致上游批次进入不同的罐中，导致批次关联出现多对多的情况</t>
+  </si>
+  <si>
+    <t>状态缺失</t>
+  </si>
+  <si>
+    <t>状态字段可能缺了一个糖化中的状态</t>
+  </si>
+  <si>
+    <t>第5层：F42中间品批次</t>
+  </si>
+  <si>
+    <t>首批生成规则</t>
+  </si>
+  <si>
+    <t>当日首个批次的起始时间生成规则：首先找到当日所有糖化罐批次尾号为001的批次，并找到这些批次中出罐时间最早的出罐时间，作为当日首批的起始时间切片；
+后续批次生成规则，按照过程时间依次首尾相接的向后推导，直到次日最早的批次</t>
+  </si>
+  <si>
+    <t>批次构成和关联</t>
+  </si>
+  <si>
+    <t>批次构成以及和上游关联：在批次起始时间记录所有糖化罐的液位，在批次结束时间记录所有糖化罐的液位，计算所有液位差值，根据上游糖化罐出料批次计算当前批次所有的上游批次构成例如TH03-001（40吨）、TH04-002（35吨）、TH05-002（25吨）</t>
+  </si>
+  <si>
+    <t>向下游分离比例</t>
+  </si>
+  <si>
+    <t>分离比例是手动调整的吗？分离比例变化频率是什么？</t>
+  </si>
+  <si>
+    <t>下游总产出量</t>
+  </si>
+  <si>
+    <t>产出F42比例，是否有收率？</t>
+  </si>
+  <si>
+    <t>第6层：色谱分离</t>
+  </si>
+  <si>
+    <t>树脂</t>
+  </si>
+  <si>
+    <t>树脂的使用周期怎么定义？怎么折算成本？</t>
+  </si>
+  <si>
+    <t>色谱分离工艺前是有阀门吗？
+阀门状态的切换依据是什么？
+时间窗起点是否以阀门切换至开的时间计算？</t>
+  </si>
+  <si>
+    <t>第7层：色谱分离</t>
+  </si>
+  <si>
+    <t>滤板</t>
+  </si>
+  <si>
+    <t>人工更换的滤板成本怎么计算？</t>
+  </si>
+  <si>
+    <t>入口时间</t>
+  </si>
+  <si>
+    <t>DCS记录每批物料的入口时间，怎么判断每个批次的起点？</t>
+  </si>
+  <si>
+    <t>多批次的量</t>
+  </si>
+  <si>
+    <t>当前批次同时来源于两个批次第5和第6，怎么判断来源两个批次的量？</t>
+  </si>
+  <si>
+    <t>切割规则</t>
+  </si>
+  <si>
+    <t>切割规则中的2小时一个批次是依据什么设定的？</t>
+  </si>
+  <si>
+    <t>配方切换</t>
+  </si>
+  <si>
+    <t>配方切换是立刻完成的吗？即配方切换时刻就开始生产新配方的产品？</t>
+  </si>
+  <si>
+    <t>第8层：QC罐</t>
+  </si>
+  <si>
+    <t>质检不合格返流</t>
+  </si>
+  <si>
+    <t>质检不合格的液体会根据原因返流到对应工序？返回后的处理是什么？
+暂停其他的料的进入优先处理返流的不合格料，还是有其他隔离手段？</t>
+  </si>
+  <si>
+    <t>第9层：成品罐</t>
+  </si>
+  <si>
+    <t>返流到QC罐</t>
+  </si>
+  <si>
+    <t>残留的液体会返回QC罐，然后再质检再判断是否继续返流到其他工艺流程还是回到成本罐，返回QC罐的流程是什么？返回的QC罐未满是继续装新批次的糖还是先判断完质量，分配好后续去向再继续装新批次的液体？</t>
+  </si>
+  <si>
+    <t>第10.1层：小包装</t>
+  </si>
+  <si>
+    <t>小包装</t>
+  </si>
+  <si>
+    <t>对于使用果糖成品继续加工的小包装产品，是否只剩下了分装的过程？这部分批次应该增加到整个批次管理流程里</t>
   </si>
 </sst>
 </file>
@@ -708,7 +925,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -753,19 +970,6 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
       <top style="thin">
         <color auto="1"/>
       </top>
@@ -787,6 +991,32 @@
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -913,7 +1143,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -925,34 +1155,34 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1037,7 +1267,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1053,17 +1283,32 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1404,17 +1649,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G15"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="17.6" outlineLevelCol="6"/>
+  <dimension ref="A1:H47"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="17.6" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="20.8333333333333" customWidth="1"/>
-    <col min="3" max="3" width="18.6666666666667" customWidth="1"/>
-    <col min="4" max="4" width="62.8333333333333" customWidth="1"/>
-    <col min="5" max="5" width="10.8333333333333" customWidth="1"/>
-    <col min="6" max="6" width="69.8333333333333" customWidth="1"/>
+    <col min="3" max="4" width="18.6666666666667" customWidth="1"/>
+    <col min="5" max="5" width="64.8583333333333" customWidth="1"/>
+    <col min="6" max="6" width="10.8333333333333" customWidth="1"/>
+    <col min="7" max="7" width="69.8333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.35" spans="1:7">
+    <row r="1" ht="18.35" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1424,7 +1669,7 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
@@ -1433,291 +1678,922 @@
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" ht="18" spans="1:7">
-      <c r="A2" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="3" t="s">
+    </row>
+    <row r="2" ht="18" spans="1:8">
+      <c r="A2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="B2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="C2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="D2" s="3"/>
+      <c r="E2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="3"/>
-    </row>
-    <row r="3" ht="229" spans="1:7">
-      <c r="A3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="G2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="H2" s="5"/>
+    </row>
+    <row r="3" ht="229" spans="1:8">
+      <c r="A3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="C3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="4" t="s">
+      <c r="D3" s="3"/>
+      <c r="E3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="4"/>
-    </row>
-    <row r="4" ht="300" spans="1:7">
-      <c r="A4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="4" t="s">
+      <c r="F3" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="5" t="s">
+      <c r="H3" s="3"/>
+    </row>
+    <row r="4" ht="300" spans="1:8">
+      <c r="A4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="5" t="s">
+      <c r="C4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="3"/>
+      <c r="E4" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="4"/>
-    </row>
-    <row r="5" ht="18" spans="1:7">
-      <c r="A5" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="4" t="s">
+      <c r="F4" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="5" t="s">
+      <c r="H4" s="3"/>
+    </row>
+    <row r="5" ht="18" spans="1:8">
+      <c r="A5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-    </row>
-    <row r="6" ht="88" spans="1:7">
-      <c r="A6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="4" t="s">
+      <c r="C5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="3"/>
+      <c r="E5" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="F5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+    </row>
+    <row r="6" ht="88" spans="1:8">
+      <c r="A6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="C6" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-    </row>
-    <row r="7" ht="36" spans="1:7">
-      <c r="A7" s="4" t="s">
+      <c r="D6" s="3"/>
+      <c r="E6" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="F6" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+    </row>
+    <row r="7" ht="36" spans="1:8">
+      <c r="A7" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="5" t="s">
+      <c r="C7" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="8"/>
+      <c r="E7" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="4"/>
-    </row>
-    <row r="8" ht="141" spans="1:7">
-      <c r="A8" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8" s="4" t="s">
+      <c r="F7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" s="5" t="s">
+      <c r="H7" s="3"/>
+    </row>
+    <row r="8" ht="141" spans="1:8">
+      <c r="A8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="4" t="s">
+      <c r="C8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="3"/>
+      <c r="E8" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="G8" s="4"/>
-    </row>
-    <row r="9" ht="141" spans="1:7">
-      <c r="A9" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="4" t="s">
+      <c r="F8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="5" t="s">
+      <c r="H8" s="3"/>
+    </row>
+    <row r="9" ht="141" spans="1:8">
+      <c r="A9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E9" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="5" t="s">
+      <c r="C9" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="8"/>
+      <c r="E9" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="G9" s="4"/>
-    </row>
-    <row r="10" ht="53" spans="1:7">
-      <c r="A10" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10" s="4" t="s">
+      <c r="F9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="5" t="s">
+      <c r="H9" s="3"/>
+    </row>
+    <row r="10" ht="53" spans="1:8">
+      <c r="A10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="E10" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" s="5" t="s">
+      <c r="C10" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="8"/>
+      <c r="E10" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="G10" s="4"/>
-    </row>
-    <row r="11" ht="36" spans="1:7">
-      <c r="A11" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="4" t="s">
+      <c r="F10" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D11" s="5" t="s">
+      <c r="H10" s="3"/>
+    </row>
+    <row r="11" ht="36" spans="1:8">
+      <c r="A11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" s="5" t="s">
+      <c r="C11" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="3"/>
+      <c r="E11" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="G11" s="4"/>
-    </row>
-    <row r="12" ht="176" spans="1:7">
-      <c r="A12" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B12" s="4" t="s">
+      <c r="F11" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12" s="5" t="s">
+      <c r="H11" s="3"/>
+    </row>
+    <row r="12" ht="176" spans="1:8">
+      <c r="A12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="E12" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" s="4" t="s">
+      <c r="C12" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G12" s="4"/>
-    </row>
-    <row r="13" ht="18" spans="1:7">
-      <c r="A13" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" s="4" t="s">
+      <c r="F12" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" s="5" t="s">
+      <c r="H12" s="3"/>
+    </row>
+    <row r="13" ht="18" spans="1:8">
+      <c r="A13" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="C13" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="F13" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="G13" s="4"/>
-    </row>
-    <row r="14" ht="36" spans="1:6">
-      <c r="A14" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" s="4" t="s">
+      <c r="H13" s="3"/>
+    </row>
+    <row r="14" ht="36" spans="1:8">
+      <c r="A14" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D14" s="5" t="s">
+      <c r="C14" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="3"/>
+      <c r="E14" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="E14" s="4"/>
-      <c r="F14" s="5"/>
-    </row>
-    <row r="15" ht="408" customHeight="1" spans="1:6">
-      <c r="A15" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="4" t="s">
+      <c r="F14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D15" s="5" t="s">
+    </row>
+    <row r="15" ht="408" customHeight="1" spans="1:8">
+      <c r="A15" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="E15" s="4"/>
-      <c r="F15" s="5" t="s">
+      <c r="C15" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="10"/>
+      <c r="E15" s="11" t="s">
         <v>52</v>
       </c>
+      <c r="F15" s="10"/>
+      <c r="G15" s="11" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="16" ht="18" spans="1:8">
+      <c r="A16" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="12"/>
+    </row>
+    <row r="17" ht="36" spans="1:8">
+      <c r="A17" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="12"/>
+    </row>
+    <row r="18" ht="71" spans="1:8">
+      <c r="A18" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="12"/>
+    </row>
+    <row r="20" ht="36" spans="1:8">
+      <c r="A20" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
+    </row>
+    <row r="21" ht="36" spans="1:8">
+      <c r="A21" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="E21" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="12"/>
+    </row>
+    <row r="22" ht="53" spans="1:8">
+      <c r="A22" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="12"/>
+    </row>
+    <row r="23" ht="18" spans="1:8">
+      <c r="A23" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="E24" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+    </row>
+    <row r="25" ht="71" spans="1:8">
+      <c r="A25" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="F25" s="12"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="12"/>
+    </row>
+    <row r="26" ht="36" spans="1:8">
+      <c r="A26" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="E26" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="12"/>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="E27" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="12"/>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="E28" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="F28" s="12"/>
+      <c r="G28" s="12"/>
+      <c r="H28" s="12"/>
+    </row>
+    <row r="29" ht="36" spans="1:8">
+      <c r="A29" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D29" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="F29" s="12"/>
+      <c r="G29" s="12"/>
+      <c r="H29" s="12"/>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D30" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="E30" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12"/>
+    </row>
+    <row r="31" ht="88" spans="1:8">
+      <c r="A31" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="F31" s="12"/>
+      <c r="G31" s="12"/>
+      <c r="H31" s="12"/>
+    </row>
+    <row r="32" ht="71" spans="1:8">
+      <c r="A32" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D32" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="E32" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="12"/>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B33" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="E33" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="F33" s="12"/>
+      <c r="G33" s="12"/>
+      <c r="H33" s="12"/>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D34" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E34" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="F34" s="12"/>
+      <c r="G34" s="12"/>
+      <c r="H34" s="12"/>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="E35" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="F35" s="12"/>
+      <c r="G35" s="12"/>
+      <c r="H35" s="12"/>
+    </row>
+    <row r="36" ht="53" spans="1:8">
+      <c r="A36" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B36" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="C36" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="E36" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="F36" s="12"/>
+      <c r="G36" s="12"/>
+      <c r="H36" s="12"/>
+    </row>
+    <row r="37" ht="18" spans="1:8">
+      <c r="A37" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D37" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="E37" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="F37" s="12"/>
+      <c r="G37" s="12"/>
+      <c r="H37" s="12"/>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="E38" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="F38" s="12"/>
+      <c r="G38" s="12"/>
+      <c r="H38" s="12"/>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="E39" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="F39" s="12"/>
+      <c r="G39" s="12"/>
+      <c r="H39" s="12"/>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="C40" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D40" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="E40" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="F40" s="12"/>
+      <c r="G40" s="12"/>
+      <c r="H40" s="12"/>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B41" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="C41" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D41" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="E41" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="F41" s="12"/>
+      <c r="G41" s="12"/>
+      <c r="H41" s="12"/>
+    </row>
+    <row r="42" ht="36" spans="1:8">
+      <c r="A42" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B42" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="C42" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D42" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="E42" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="F42" s="12"/>
+      <c r="G42" s="12"/>
+      <c r="H42" s="12"/>
+    </row>
+    <row r="43" ht="53" spans="1:8">
+      <c r="A43" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B43" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="C43" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D43" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="E43" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="F43" s="12"/>
+      <c r="G43" s="12"/>
+      <c r="H43" s="12"/>
+    </row>
+    <row r="44" ht="36" spans="1:8">
+      <c r="A44" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B44" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="C44" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D44" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="E44" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="F44" s="12"/>
+      <c r="G44" s="12"/>
+      <c r="H44" s="12"/>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" s="12"/>
+      <c r="B45" s="12"/>
+      <c r="C45" s="12"/>
+      <c r="D45" s="12"/>
+      <c r="E45" s="12"/>
+      <c r="F45" s="12"/>
+      <c r="G45" s="12"/>
+      <c r="H45" s="12"/>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" s="12"/>
+      <c r="B46" s="12"/>
+      <c r="C46" s="12"/>
+      <c r="D46" s="12"/>
+      <c r="E46" s="12"/>
+      <c r="F46" s="12"/>
+      <c r="G46" s="12"/>
+      <c r="H46" s="12"/>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" s="12"/>
+      <c r="B47" s="12"/>
+      <c r="C47" s="12"/>
+      <c r="D47" s="12"/>
+      <c r="E47" s="12"/>
+      <c r="F47" s="12"/>
+      <c r="G47" s="12"/>
+      <c r="H47" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/1-wiki-资料沉淀/业务调研事项记录.xlsx
+++ b/1-wiki-资料沉淀/业务调研事项记录.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="131">
   <si>
     <t>业务模块</t>
   </si>
@@ -342,11 +342,19 @@
     <t>每一批物料在各工艺产出的质量怎么获取？收率是怎么获取？</t>
   </si>
   <si>
-    <t>糖化罐和QC罐进出</t>
-  </si>
-  <si>
-    <t>12个糖化罐是同时排出还是依次排出？
-QC罐是同时进料还是依次进料？</t>
+    <t>投料口和各罐进出方式</t>
+  </si>
+  <si>
+    <t>投料口数量是多少？
+12个糖化罐是同时进料还是依次进料？同时排出还是依次排出？依次是否有优先级？
+QC罐是同时进料还是依次进料？同时排出还是依次排出？依次是否有优先级？
+成品罐是同时进料还是依次进料？同时排出还是依次排出？依次是否有优先级？</t>
+  </si>
+  <si>
+    <t>投料口：一共8个，同时投料。
+糖化罐：依次进，依次排，DCS控制顺序
+QC罐：依次进，依次出，DCS控制顺序
+成品罐：依次进，依次出，DCS控制顺序</t>
   </si>
   <si>
     <t>流量</t>
@@ -448,10 +456,16 @@
 后续批次生成规则，按照过程时间依次首尾相接的向后推导，直到次日最早的批次</t>
   </si>
   <si>
+    <t>如果是糖化罐依次初，规则会出现变化</t>
+  </si>
+  <si>
     <t>批次构成和关联</t>
   </si>
   <si>
     <t>批次构成以及和上游关联：在批次起始时间记录所有糖化罐的液位，在批次结束时间记录所有糖化罐的液位，计算所有液位差值，根据上游糖化罐出料批次计算当前批次所有的上游批次构成例如TH03-001（40吨）、TH04-002（35吨）、TH05-002（25吨）</t>
+  </si>
+  <si>
+    <t>如果是糖化罐依次进，规则会出现变化</t>
   </si>
   <si>
     <t>向下游分离比例</t>
@@ -516,10 +530,10 @@
     <t>第8层：QC罐</t>
   </si>
   <si>
-    <t>质检不合格返流</t>
-  </si>
-  <si>
-    <t>质检不合格的液体会根据原因返流到对应工序？返回后的处理是什么？
+    <t>质检不合格冻结和返流</t>
+  </si>
+  <si>
+    <t>质检不合格的液体做冻结时是实物上的冻结吗？然后返流会根据原因返流到对应工序吗？返回后的处理是什么？
 暂停其他的料的进入优先处理返流的不合格料，还是有其他隔离手段？</t>
   </si>
   <si>
@@ -530,6 +544,24 @@
   </si>
   <si>
     <t>残留的液体会返回QC罐，然后再质检再判断是否继续返流到其他工艺流程还是回到成本罐，返回QC罐的流程是什么？返回的QC罐未满是继续装新批次的糖还是先判断完质量，分配好后续去向再继续装新批次的液体？</t>
+  </si>
+  <si>
+    <t>成品罐状态</t>
+  </si>
+  <si>
+    <t>进罐状态需要增加空罐和出货中</t>
+  </si>
+  <si>
+    <t>第10层：车次</t>
+  </si>
+  <si>
+    <t>签收状态</t>
+  </si>
+  <si>
+    <t>部分签收的含义是什么？实际会怎么签收</t>
+  </si>
+  <si>
+    <t>除了销售订单号外，还需要生成发货单号</t>
   </si>
   <si>
     <t>第10.1层：小包装</t>
@@ -1267,7 +1299,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1292,9 +1324,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1303,9 +1332,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1649,12 +1675,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="17.6" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="20.8333333333333" customWidth="1"/>
-    <col min="3" max="4" width="18.6666666666667" customWidth="1"/>
-    <col min="5" max="5" width="64.8583333333333" customWidth="1"/>
+    <col min="3" max="3" width="18.6666666666667" customWidth="1"/>
+    <col min="4" max="4" width="22.7333333333333" customWidth="1"/>
+    <col min="5" max="5" width="66.1083333333333" customWidth="1"/>
     <col min="6" max="6" width="10.8333333333333" customWidth="1"/>
     <col min="7" max="7" width="69.8333333333333" customWidth="1"/>
   </cols>
@@ -1801,7 +1828,7 @@
       <c r="C7" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="8"/>
+      <c r="D7" s="5"/>
       <c r="E7" s="7" t="s">
         <v>28</v>
       </c>
@@ -1845,7 +1872,7 @@
       <c r="C9" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="8"/>
+      <c r="D9" s="5"/>
       <c r="E9" s="7" t="s">
         <v>34</v>
       </c>
@@ -1867,7 +1894,7 @@
       <c r="C10" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="8"/>
+      <c r="D10" s="5"/>
       <c r="E10" s="7" t="s">
         <v>37</v>
       </c>
@@ -1940,7 +1967,7 @@
       <c r="F13" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G13" s="9" t="s">
+      <c r="G13" s="8" t="s">
         <v>47</v>
       </c>
       <c r="H13" s="3"/>
@@ -1967,633 +1994,699 @@
       </c>
     </row>
     <row r="15" ht="408" customHeight="1" spans="1:8">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D15" s="10"/>
-      <c r="E15" s="11" t="s">
+      <c r="D15" s="9"/>
+      <c r="E15" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="F15" s="10"/>
-      <c r="G15" s="11" t="s">
+      <c r="F15" s="9"/>
+      <c r="G15" s="10" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:8">
-      <c r="A16" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B16" s="12" t="s">
+      <c r="A16" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C16" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="D16" s="12" t="s">
+      <c r="C16" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="E16" s="13" t="s">
+      <c r="E16" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="12"/>
-    </row>
-    <row r="17" ht="36" spans="1:8">
-      <c r="A17" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B17" s="12" t="s">
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+    </row>
+    <row r="17" ht="124" spans="1:8">
+      <c r="A17" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C17" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="D17" s="12" t="s">
+      <c r="C17" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E17" s="13" t="s">
+      <c r="E17" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="12"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="H17" s="3"/>
     </row>
     <row r="18" ht="71" spans="1:8">
-      <c r="A18" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B18" s="12" t="s">
+      <c r="A18" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C18" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="D18" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="E18" s="13" t="s">
+      <c r="C18" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="12"/>
+      <c r="E18" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B19" s="12" t="s">
+      <c r="A19" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C19" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="E19" s="12" t="s">
+      <c r="C19" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
+      <c r="E19" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
     </row>
     <row r="20" ht="36" spans="1:8">
-      <c r="A20" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B20" s="12" t="s">
+      <c r="A20" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C20" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="E20" s="13" t="s">
+      <c r="C20" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="12"/>
+      <c r="E20" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
     </row>
     <row r="21" ht="36" spans="1:8">
-      <c r="A21" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B21" s="12" t="s">
+      <c r="A21" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C21" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="E21" s="13" t="s">
+      <c r="C21" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="12"/>
+      <c r="E21" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
     </row>
     <row r="22" ht="53" spans="1:8">
-      <c r="A22" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B22" s="12" t="s">
+      <c r="A22" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C22" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="E22" s="13" t="s">
+      <c r="C22" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="12"/>
+      <c r="E22" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
     </row>
     <row r="23" ht="18" spans="1:8">
-      <c r="A23" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="C23" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="D23" s="12" t="s">
+      <c r="A23" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="E23" s="13" t="s">
+      <c r="C23" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="F23" s="12"/>
-      <c r="G23" s="12"/>
-      <c r="H23" s="12"/>
+      <c r="E23" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="E24" s="12" t="s">
+      <c r="A24" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="F24" s="12"/>
-      <c r="G24" s="12"/>
-      <c r="H24" s="12"/>
+      <c r="E24" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
     </row>
     <row r="25" ht="71" spans="1:8">
-      <c r="A25" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="E25" s="13" t="s">
+      <c r="A25" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D25" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="F25" s="12"/>
-      <c r="G25" s="12"/>
-      <c r="H25" s="12"/>
+      <c r="E25" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
     </row>
     <row r="26" ht="36" spans="1:8">
-      <c r="A26" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B26" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="D26" s="12" t="s">
+      <c r="A26" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E26" s="13" t="s">
+      <c r="C26" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="F26" s="12"/>
-      <c r="G26" s="12"/>
-      <c r="H26" s="12"/>
+      <c r="E26" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
     </row>
     <row r="27" spans="1:8">
-      <c r="A27" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B27" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="C27" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="D27" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="E27" s="12" t="s">
+      <c r="A27" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D27" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="F27" s="12"/>
-      <c r="G27" s="12"/>
-      <c r="H27" s="12"/>
+      <c r="E27" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
     </row>
     <row r="28" spans="1:8">
-      <c r="A28" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B28" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="C28" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="D28" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="E28" s="12" t="s">
+      <c r="A28" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D28" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="F28" s="12"/>
-      <c r="G28" s="12"/>
-      <c r="H28" s="12"/>
+      <c r="E28" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
     </row>
     <row r="29" ht="36" spans="1:8">
-      <c r="A29" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B29" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="C29" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="D29" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="E29" s="13" t="s">
+      <c r="A29" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D29" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="F29" s="12"/>
-      <c r="G29" s="12"/>
-      <c r="H29" s="12"/>
+      <c r="E29" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
     </row>
     <row r="30" spans="1:8">
-      <c r="A30" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B30" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="C30" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="D30" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="E30" s="12" t="s">
+      <c r="A30" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D30" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="F30" s="12"/>
-      <c r="G30" s="12"/>
-      <c r="H30" s="12"/>
+      <c r="E30" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
     </row>
     <row r="31" ht="88" spans="1:8">
-      <c r="A31" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B31" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="C31" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="D31" s="12" t="s">
+      <c r="A31" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="E31" s="13" t="s">
+      <c r="C31" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D31" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="F31" s="12"/>
-      <c r="G31" s="12"/>
-      <c r="H31" s="12"/>
+      <c r="E31" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="H31" s="3"/>
     </row>
     <row r="32" ht="71" spans="1:8">
-      <c r="A32" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B32" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="C32" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="D32" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="E32" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="F32" s="12"/>
-      <c r="G32" s="12"/>
-      <c r="H32" s="12"/>
+      <c r="A32" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H32" s="3"/>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B33" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="C33" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="D33" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="E33" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="F33" s="12"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="12"/>
+      <c r="A33" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B34" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="C34" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="D34" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="E34" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="F34" s="12"/>
-      <c r="G34" s="12"/>
-      <c r="H34" s="12"/>
+      <c r="A34" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="3"/>
     </row>
     <row r="35" spans="1:8">
-      <c r="A35" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B35" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="C35" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="D35" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="E35" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="F35" s="12"/>
-      <c r="G35" s="12"/>
-      <c r="H35" s="12"/>
+      <c r="A35" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="3"/>
     </row>
     <row r="36" ht="53" spans="1:8">
-      <c r="A36" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B36" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="C36" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="D36" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="E36" s="13" t="s">
+      <c r="A36" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="F36" s="12"/>
-      <c r="G36" s="12"/>
-      <c r="H36" s="12"/>
+      <c r="C36" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="3"/>
     </row>
     <row r="37" ht="18" spans="1:8">
-      <c r="A37" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B37" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="C37" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="D37" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="E37" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="F37" s="12"/>
-      <c r="G37" s="12"/>
-      <c r="H37" s="12"/>
+      <c r="A37" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="3"/>
     </row>
     <row r="38" spans="1:8">
-      <c r="A38" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B38" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="C38" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="D38" s="12" t="s">
+      <c r="A38" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="E38" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="F38" s="12"/>
-      <c r="G38" s="12"/>
-      <c r="H38" s="12"/>
+      <c r="C38" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="3"/>
     </row>
     <row r="39" spans="1:8">
-      <c r="A39" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B39" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="C39" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="D39" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="E39" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="F39" s="12"/>
-      <c r="G39" s="12"/>
-      <c r="H39" s="12"/>
+      <c r="A39" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
+      <c r="H39" s="3"/>
     </row>
     <row r="40" spans="1:8">
-      <c r="A40" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B40" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="C40" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="D40" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="E40" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="F40" s="12"/>
-      <c r="G40" s="12"/>
-      <c r="H40" s="12"/>
+      <c r="A40" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+      <c r="H40" s="3"/>
     </row>
     <row r="41" spans="1:8">
-      <c r="A41" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B41" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="C41" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="D41" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="E41" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="F41" s="12"/>
-      <c r="G41" s="12"/>
-      <c r="H41" s="12"/>
-    </row>
-    <row r="42" ht="36" spans="1:8">
-      <c r="A42" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B42" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="C42" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="D42" s="12" t="s">
+      <c r="A41" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D41" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="E42" s="13" t="s">
+      <c r="E41" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="F42" s="12"/>
-      <c r="G42" s="12"/>
-      <c r="H42" s="12"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
+      <c r="H41" s="3"/>
+    </row>
+    <row r="42" ht="53" spans="1:8">
+      <c r="A42" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
+      <c r="H42" s="3"/>
     </row>
     <row r="43" ht="53" spans="1:8">
-      <c r="A43" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B43" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="C43" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="D43" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="E43" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="F43" s="12"/>
-      <c r="G43" s="12"/>
-      <c r="H43" s="12"/>
-    </row>
-    <row r="44" ht="36" spans="1:8">
-      <c r="A44" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B44" s="12" t="s">
+      <c r="A43" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B43" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="C44" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="D44" s="12" t="s">
+      <c r="C43" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D43" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="E44" s="13" t="s">
+      <c r="E43" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="F44" s="12"/>
-      <c r="G44" s="12"/>
-      <c r="H44" s="12"/>
-    </row>
-    <row r="45" spans="1:8">
-      <c r="A45" s="12"/>
-      <c r="B45" s="12"/>
-      <c r="C45" s="12"/>
-      <c r="D45" s="12"/>
-      <c r="E45" s="12"/>
-      <c r="F45" s="12"/>
-      <c r="G45" s="12"/>
-      <c r="H45" s="12"/>
-    </row>
-    <row r="46" spans="1:8">
-      <c r="A46" s="12"/>
-      <c r="B46" s="12"/>
-      <c r="C46" s="12"/>
-      <c r="D46" s="12"/>
-      <c r="E46" s="12"/>
-      <c r="F46" s="12"/>
-      <c r="G46" s="12"/>
-      <c r="H46" s="12"/>
-    </row>
-    <row r="47" spans="1:8">
-      <c r="A47" s="12"/>
-      <c r="B47" s="12"/>
-      <c r="C47" s="12"/>
-      <c r="D47" s="12"/>
-      <c r="E47" s="12"/>
-      <c r="F47" s="12"/>
-      <c r="G47" s="12"/>
-      <c r="H47" s="12"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
+      <c r="H43" s="3"/>
+    </row>
+    <row r="44" ht="18" spans="1:8">
+      <c r="A44" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
+      <c r="H44" s="3"/>
+    </row>
+    <row r="45" ht="18" spans="1:8">
+      <c r="A45" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
+      <c r="H45" s="3"/>
+    </row>
+    <row r="46" ht="18" spans="1:8">
+      <c r="A46" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
+      <c r="H46" s="3"/>
+    </row>
+    <row r="47" ht="36" spans="1:8">
+      <c r="A47" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="F47" s="3"/>
+      <c r="G47" s="3"/>
+      <c r="H47" s="3"/>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" s="3"/>
+      <c r="B48" s="3"/>
+      <c r="C48" s="3"/>
+      <c r="D48" s="3"/>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3"/>
+      <c r="H48" s="3"/>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" s="3"/>
+      <c r="B49" s="3"/>
+      <c r="C49" s="3"/>
+      <c r="D49" s="3"/>
+      <c r="E49" s="3"/>
+      <c r="F49" s="3"/>
+      <c r="G49" s="3"/>
+      <c r="H49" s="3"/>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" s="3"/>
+      <c r="B50" s="3"/>
+      <c r="C50" s="3"/>
+      <c r="D50" s="3"/>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3"/>
+      <c r="H50" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/1-wiki-资料沉淀/业务调研事项记录.xlsx
+++ b/1-wiki-资料沉淀/业务调研事项记录.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="133">
   <si>
     <t>业务模块</t>
   </si>
@@ -342,6 +342,10 @@
     <t>每一批物料在各工艺产出的质量怎么获取？收率是怎么获取？</t>
   </si>
   <si>
+    <t>算出来
+来源QMS，LIMS</t>
+  </si>
+  <si>
     <t>投料口和各罐进出方式</t>
   </si>
   <si>
@@ -398,6 +402,9 @@
   </si>
   <si>
     <t>投料口后的三个罐（溶粉罐、乳罐、接收罐）是否有必要建立批次？</t>
+  </si>
+  <si>
+    <t>没必要</t>
   </si>
   <si>
     <t>投料批次连续</t>
@@ -2012,7 +2019,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="16" ht="18" spans="1:8">
+    <row r="16" ht="36" spans="1:8">
       <c r="A16" s="3" t="s">
         <v>54</v>
       </c>
@@ -2029,7 +2036,9 @@
         <v>58</v>
       </c>
       <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
+      <c r="G16" s="11" t="s">
+        <v>59</v>
+      </c>
       <c r="H16" s="3"/>
     </row>
     <row r="17" ht="124" spans="1:8">
@@ -2043,14 +2052,14 @@
         <v>56</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H17" s="3"/>
     </row>
@@ -2065,10 +2074,10 @@
         <v>56</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
@@ -2085,10 +2094,10 @@
         <v>56</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
@@ -2105,10 +2114,10 @@
         <v>56</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
@@ -2125,10 +2134,10 @@
         <v>56</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
@@ -2145,10 +2154,10 @@
         <v>56</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
@@ -2159,19 +2168,21 @@
         <v>54</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>56</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
+      <c r="G23" s="3" t="s">
+        <v>76</v>
+      </c>
       <c r="H23" s="3"/>
     </row>
     <row r="24" spans="1:8">
@@ -2179,16 +2190,16 @@
         <v>54</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>56</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
@@ -2199,16 +2210,16 @@
         <v>54</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>56</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
@@ -2219,16 +2230,16 @@
         <v>54</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>56</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
@@ -2239,16 +2250,16 @@
         <v>54</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>56</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
@@ -2259,16 +2270,16 @@
         <v>54</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>56</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
@@ -2279,16 +2290,16 @@
         <v>54</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>56</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
@@ -2299,16 +2310,16 @@
         <v>54</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>56</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
@@ -2319,20 +2330,20 @@
         <v>54</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>56</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H31" s="3"/>
     </row>
@@ -2341,20 +2352,20 @@
         <v>54</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>56</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H32" s="3"/>
     </row>
@@ -2363,16 +2374,16 @@
         <v>54</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>56</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3"/>
@@ -2383,16 +2394,16 @@
         <v>54</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>56</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3"/>
@@ -2403,16 +2414,16 @@
         <v>54</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>56</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3"/>
@@ -2423,16 +2434,16 @@
         <v>54</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>56</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3"/>
@@ -2443,16 +2454,16 @@
         <v>54</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>56</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3"/>
@@ -2463,16 +2474,16 @@
         <v>54</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>56</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3"/>
@@ -2483,16 +2494,16 @@
         <v>54</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>56</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3"/>
@@ -2503,16 +2514,16 @@
         <v>54</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>56</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3"/>
@@ -2523,16 +2534,16 @@
         <v>54</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>56</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3"/>
@@ -2543,16 +2554,16 @@
         <v>54</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>56</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3"/>
@@ -2563,16 +2574,16 @@
         <v>54</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>56</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3"/>
@@ -2583,16 +2594,16 @@
         <v>54</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>56</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3"/>
@@ -2603,16 +2614,16 @@
         <v>54</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>56</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3"/>
@@ -2623,16 +2634,16 @@
         <v>54</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>56</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3"/>
@@ -2643,16 +2654,16 @@
         <v>54</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>56</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3"/>
